--- a/salidas/empresas/AMZN.xlsx
+++ b/salidas/empresas/AMZN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1305,7 +1317,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1330,7 +1342,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1355,7 +1367,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1380,7 +1392,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1405,7 +1417,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1430,7 +1442,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1455,7 +1467,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1480,7 +1492,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1505,7 +1517,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1530,7 +1542,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1555,7 +1567,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1580,7 +1592,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1605,7 +1617,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1630,7 +1642,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1655,7 +1667,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1680,7 +1692,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1705,7 +1717,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1730,7 +1742,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1759,7 +1771,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1788,7 +1800,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1817,7 +1829,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1846,7 +1858,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1875,7 +1887,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1904,7 +1916,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1933,7 +1945,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1962,7 +1974,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1991,7 +2003,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2020,7 +2032,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2049,7 +2061,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2078,7 +2090,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2107,7 +2119,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2136,7 +2148,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2165,7 +2177,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2194,7 +2206,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2223,7 +2235,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2252,7 +2264,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2281,7 +2293,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2310,7 +2322,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2339,7 +2351,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2368,7 +2380,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2397,7 +2409,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2426,7 +2438,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2455,7 +2467,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2484,7 +2496,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2513,7 +2525,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2540,7 +2552,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2567,7 +2579,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2594,7 +2606,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2621,7 +2633,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2648,7 +2660,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2675,7 +2687,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2704,7 +2716,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2733,7 +2745,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2762,7 +2774,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2791,7 +2803,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2820,7 +2832,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2849,7 +2861,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2878,7 +2890,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2907,7 +2919,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2936,7 +2948,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2965,7 +2977,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2994,7 +3006,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3023,7 +3035,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3050,7 +3062,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3077,7 +3089,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3104,7 +3116,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3131,7 +3143,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3158,7 +3170,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3185,7 +3197,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3212,7 +3224,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3239,7 +3251,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3266,7 +3278,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3293,7 +3305,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3320,7 +3332,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3347,7 +3359,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3376,7 +3388,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3405,7 +3417,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3434,7 +3446,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3463,7 +3475,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3492,7 +3504,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3521,7 +3533,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3550,7 +3562,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3579,7 +3591,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3608,7 +3620,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3637,7 +3649,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3666,7 +3678,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3695,7 +3707,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3724,7 +3736,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3753,7 +3765,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3782,7 +3794,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3811,7 +3823,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3840,7 +3852,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3869,7 +3881,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3898,7 +3910,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3927,7 +3939,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3956,7 +3968,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3985,7 +3997,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4014,7 +4026,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4043,7 +4055,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4072,7 +4084,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4101,7 +4113,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4130,7 +4142,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4159,7 +4171,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4188,7 +4200,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4217,7 +4229,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4246,7 +4258,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4275,7 +4287,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4304,7 +4316,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4333,7 +4345,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4362,7 +4374,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4391,7 +4403,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4420,7 +4432,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4449,7 +4461,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4478,7 +4490,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4507,7 +4519,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4536,7 +4548,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4565,7 +4577,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4594,7 +4606,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4623,7 +4635,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4652,7 +4664,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4681,7 +4693,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4710,7 +4722,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4739,7 +4751,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4768,7 +4780,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4797,7 +4809,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4826,7 +4838,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4855,7 +4867,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4884,7 +4896,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4913,7 +4925,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4942,7 +4954,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4971,7 +4983,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5000,7 +5012,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5029,7 +5041,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5058,7 +5070,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5087,7 +5099,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5116,7 +5128,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5145,7 +5157,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5174,7 +5186,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5203,7 +5215,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5232,7 +5244,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5261,7 +5273,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5290,7 +5302,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5319,7 +5331,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5348,7 +5360,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5377,7 +5389,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5406,7 +5418,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5435,7 +5447,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5464,7 +5476,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5493,7 +5505,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5522,7 +5534,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5551,7 +5563,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5580,7 +5592,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5609,7 +5621,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5638,7 +5650,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5667,7 +5679,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5696,7 +5708,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5725,7 +5737,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5754,7 +5766,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5783,7 +5795,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5812,7 +5824,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5841,7 +5853,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5870,7 +5882,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5899,7 +5911,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5926,7 +5938,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5953,7 +5965,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5982,7 +5994,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6011,7 +6023,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6040,7 +6052,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6069,7 +6081,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6098,7 +6110,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6127,7 +6139,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6156,7 +6168,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6185,7 +6197,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6214,7 +6226,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6243,7 +6255,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6272,7 +6284,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6301,7 +6313,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6330,7 +6342,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6359,7 +6371,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6388,7 +6400,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6417,7 +6429,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6446,7 +6458,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6475,7 +6487,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6504,7 +6516,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6533,7 +6545,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6562,7 +6574,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6591,7 +6603,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6620,7 +6632,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6649,7 +6661,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6678,7 +6690,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6707,7 +6719,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6736,7 +6748,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6765,7 +6777,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6794,7 +6806,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6823,7 +6835,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6852,7 +6864,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6881,7 +6893,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6910,7 +6922,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6939,7 +6951,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6968,7 +6980,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6997,7 +7009,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7026,7 +7038,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7055,7 +7067,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7084,7 +7096,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7113,7 +7125,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7142,32 +7154,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>249.2700042724609</v>
+        <v>249.3800048828125</v>
       </c>
       <c r="C250" t="n">
-        <v>249.2700042724609</v>
+        <v>249.3800048828125</v>
       </c>
       <c r="D250" t="n">
-        <v>543808900</v>
+        <v>577005500</v>
       </c>
       <c r="E250" t="n">
         <v>12.43</v>
       </c>
       <c r="F250" t="n">
-        <v>20.05390219408374</v>
+        <v>20.06275180070897</v>
       </c>
       <c r="G250" t="n">
         <v>10786313572</v>
       </c>
       <c r="H250" t="n">
-        <v>2688704430176.543</v>
+        <v>2689890931252.907</v>
       </c>
       <c r="I250" t="n">
-        <v>0.05041656691788229</v>
+        <v>0.0534942263775678</v>
       </c>
     </row>
   </sheetData>
@@ -7199,75 +7211,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7303,13 +7315,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40109</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7345,13 +7357,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7387,13 +7399,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7429,13 +7441,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40109</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7471,13 +7483,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7504,7 +7516,7 @@
       <c r="I7" t="n">
         <v>0.1015</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="K7" t="n">
@@ -7517,13 +7529,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7550,7 +7562,7 @@
       <c r="I8" t="n">
         <v>0.114</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="K8" t="n">
@@ -7563,13 +7575,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40382</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7596,7 +7608,7 @@
       <c r="I9" t="n">
         <v>0.1205</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="K9" t="n">
@@ -7609,13 +7621,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40473</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7642,7 +7654,7 @@
       <c r="I10" t="n">
         <v>0.1235</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="K10" t="n">
@@ -7655,13 +7667,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7688,7 +7700,7 @@
       <c r="I11" t="n">
         <v>0.1265</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="K11" t="n">
@@ -7701,13 +7713,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7734,7 +7746,7 @@
       <c r="I12" t="n">
         <v>0.1155</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="K12" t="n">
@@ -7747,13 +7759,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7780,7 +7792,7 @@
       <c r="I13" t="n">
         <v>0.1135</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="K13" t="n">
@@ -7793,13 +7805,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7826,7 +7838,7 @@
       <c r="I14" t="n">
         <v>0.095</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="K14" t="n">
@@ -7839,13 +7851,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7872,7 +7884,7 @@
       <c r="I15" t="n">
         <v>0.06850000000000001</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="K15" t="n">
@@ -7885,13 +7897,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7918,7 +7930,7 @@
       <c r="I16" t="n">
         <v>0.0605</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="K16" t="n">
@@ -7931,13 +7943,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7964,7 +7976,7 @@
       <c r="I17" t="n">
         <v>0.0405</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="K17" t="n">
@@ -7977,13 +7989,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8010,7 +8022,7 @@
       <c r="I18" t="n">
         <v>0.003500000000000007</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="K18" t="n">
@@ -8023,13 +8035,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41304</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8056,7 +8068,7 @@
       <c r="I19" t="n">
         <v>0.003500000000000003</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41304</v>
       </c>
       <c r="K19" t="n">
@@ -8069,13 +8081,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8102,7 +8114,7 @@
       <c r="I20" t="n">
         <v>-0.0015</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="K20" t="n">
@@ -8115,13 +8127,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8148,7 +8160,7 @@
       <c r="I21" t="n">
         <v>-0.003</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="K21" t="n">
@@ -8161,13 +8173,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8194,7 +8206,7 @@
       <c r="I22" t="n">
         <v>0.0225</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="K22" t="n">
@@ -8207,13 +8219,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8240,7 +8252,7 @@
       <c r="I23" t="n">
         <v>0.029</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="K23" t="n">
@@ -8253,13 +8265,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8286,7 +8298,7 @@
       <c r="I24" t="n">
         <v>0.0315</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="K24" t="n">
@@ -8299,13 +8311,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8332,7 +8344,7 @@
       <c r="I25" t="n">
         <v>0.019</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="K25" t="n">
@@ -8345,13 +8357,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8378,7 +8390,7 @@
       <c r="I26" t="n">
         <v>-0.024</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="K26" t="n">
@@ -8391,13 +8403,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42034</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8424,7 +8436,7 @@
       <c r="I27" t="n">
         <v>-0.027</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42034</v>
       </c>
       <c r="K27" t="n">
@@ -8437,13 +8449,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8470,7 +8482,7 @@
       <c r="I28" t="n">
         <v>-0.0445</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="K28" t="n">
@@ -8483,13 +8495,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8516,7 +8528,7 @@
       <c r="I29" t="n">
         <v>-0.0215</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="K29" t="n">
@@ -8529,13 +8541,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8562,7 +8574,7 @@
       <c r="I30" t="n">
         <v>0.0345</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="K30" t="n">
@@ -8575,13 +8587,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42398</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8608,7 +8620,7 @@
       <c r="I31" t="n">
         <v>0.06200000000000001</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42398</v>
       </c>
       <c r="K31" t="n">
@@ -8621,13 +8633,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8654,7 +8666,7 @@
       <c r="I32" t="n">
         <v>0.1215</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="K32" t="n">
@@ -8667,13 +8679,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8700,7 +8712,7 @@
       <c r="I33" t="n">
         <v>0.201</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="K33" t="n">
@@ -8713,13 +8725,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8746,7 +8758,7 @@
       <c r="I34" t="n">
         <v>0.2185</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="K34" t="n">
@@ -8759,13 +8771,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42776</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8792,7 +8804,7 @@
       <c r="I35" t="n">
         <v>0.2455</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42776</v>
       </c>
       <c r="K35" t="n">
@@ -8805,13 +8817,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8838,7 +8850,7 @@
       <c r="I36" t="n">
         <v>0.266</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="K36" t="n">
@@ -8851,13 +8863,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8884,7 +8896,7 @@
       <c r="I37" t="n">
         <v>0.197</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="K37" t="n">
@@ -8897,13 +8909,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8930,7 +8942,7 @@
       <c r="I38" t="n">
         <v>0.197</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K38" t="n">
@@ -8943,13 +8955,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8976,7 +8988,7 @@
       <c r="I39" t="n">
         <v>0.3075</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="K39" t="n">
@@ -8989,13 +9001,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9022,7 +9034,7 @@
       <c r="I40" t="n">
         <v>0.397</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="K40" t="n">
@@ -9035,13 +9047,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9068,7 +9080,7 @@
       <c r="I41" t="n">
         <v>0.6305000000000001</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="K41" t="n">
@@ -9081,13 +9093,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9114,7 +9126,7 @@
       <c r="I42" t="n">
         <v>0.8919999999999999</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="K42" t="n">
@@ -9127,13 +9139,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9160,7 +9172,7 @@
       <c r="I43" t="n">
         <v>1.0065</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="K43" t="n">
@@ -9173,13 +9185,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9206,7 +9218,7 @@
       <c r="I44" t="n">
         <v>1.1975</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="K44" t="n">
@@ -9219,13 +9231,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9252,7 +9264,7 @@
       <c r="I45" t="n">
         <v>1.205</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="K45" t="n">
@@ -9265,13 +9277,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9298,7 +9310,7 @@
       <c r="I46" t="n">
         <v>1.129</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="K46" t="n">
@@ -9311,13 +9323,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9344,7 +9356,7 @@
       <c r="I47" t="n">
         <v>1.1505</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="K47" t="n">
@@ -9357,13 +9369,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9390,7 +9402,7 @@
       <c r="I48" t="n">
         <v>1.0465</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K48" t="n">
@@ -9403,13 +9415,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9436,7 +9448,7 @@
       <c r="I49" t="n">
         <v>1.3005</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K49" t="n">
@@ -9449,13 +9461,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9482,7 +9494,7 @@
       <c r="I50" t="n">
         <v>1.7075</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K50" t="n">
@@ -9495,13 +9507,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44230</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9528,7 +9540,7 @@
       <c r="I51" t="n">
         <v>2.0885</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44230</v>
       </c>
       <c r="K51" t="n">
@@ -9541,13 +9553,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9574,7 +9586,7 @@
       <c r="I52" t="n">
         <v>2.6275</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K52" t="n">
@@ -9587,13 +9599,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9620,7 +9632,7 @@
       <c r="I53" t="n">
         <v>2.8685</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="K53" t="n">
@@ -9633,13 +9645,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9666,7 +9678,7 @@
       <c r="I54" t="n">
         <v>2.556</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="K54" t="n">
@@ -9679,13 +9691,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9712,7 +9724,7 @@
       <c r="I55" t="n">
         <v>3.2405</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="K55" t="n">
@@ -9725,13 +9737,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9758,7 +9770,7 @@
       <c r="I56" t="n">
         <v>2.073</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K56" t="n">
@@ -9771,13 +9783,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9804,7 +9816,7 @@
       <c r="I57" t="n">
         <v>1.117</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K57" t="n">
@@ -9817,13 +9829,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9850,7 +9862,7 @@
       <c r="I58" t="n">
         <v>1.091</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K58" t="n">
@@ -9863,13 +9875,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9896,7 +9908,7 @@
       <c r="I59" t="n">
         <v>-0.27</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="K59" t="n">
@@ -9909,13 +9921,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9942,7 +9954,7 @@
       <c r="I60" t="n">
         <v>0.418</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="K60" t="n">
@@ -9955,13 +9967,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9988,7 +10000,7 @@
       <c r="I61" t="n">
         <v>1.268</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K61" t="n">
@@ -10001,13 +10013,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10034,7 +10046,7 @@
       <c r="I62" t="n">
         <v>1.928</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="K62" t="n">
@@ -10047,13 +10059,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10080,7 +10092,7 @@
       <c r="I63" t="n">
         <v>2.9</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="K63" t="n">
@@ -10093,13 +10105,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10126,7 +10138,7 @@
       <c r="I64" t="n">
         <v>3.57</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K64" t="n">
@@ -10139,13 +10151,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10172,7 +10184,7 @@
       <c r="I65" t="n">
         <v>4.18</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K65" t="n">
@@ -10185,13 +10197,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10218,7 +10230,7 @@
       <c r="I66" t="n">
         <v>4.67</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K66" t="n">
@@ -10231,13 +10243,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10264,7 +10276,7 @@
       <c r="I67" t="n">
         <v>5.53</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="K67" t="n">
@@ -10277,13 +10289,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10310,7 +10322,7 @@
       <c r="I68" t="n">
         <v>6.140000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="K68" t="n">
@@ -10323,13 +10335,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10356,7 +10368,7 @@
       <c r="I69" t="n">
         <v>6.56</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K69" t="n">
@@ -10369,13 +10381,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10402,7 +10414,7 @@
       <c r="I70" t="n">
         <v>7.08</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K70" t="n">
@@ -10415,13 +10427,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10448,7 +10460,7 @@
       <c r="I71" t="n">
         <v>7.17</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="K71" t="n">
@@ -10461,13 +10473,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10494,7 +10506,7 @@
       <c r="I72" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K72" t="n">
@@ -10507,13 +10519,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10540,7 +10552,7 @@
       <c r="I73" t="n">
         <v>12.43</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K73" t="n">
@@ -10577,52 +10589,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40011</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="C2" t="n">
@@ -10651,10 +10663,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40105</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40109</v>
       </c>
       <c r="C3" t="n">
@@ -10683,10 +10695,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40200</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40207</v>
       </c>
       <c r="C4" t="n">
@@ -10715,10 +10727,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40284</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="C5" t="n">
@@ -10747,10 +10759,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40374</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40382</v>
       </c>
       <c r="C6" t="n">
@@ -10779,10 +10791,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40465</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40473</v>
       </c>
       <c r="C7" t="n">
@@ -10811,10 +10823,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40562</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="C8" t="n">
@@ -10843,10 +10855,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40652</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="C9" t="n">
@@ -10875,10 +10887,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40739</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="C10" t="n">
@@ -10907,10 +10919,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40830</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="C11" t="n">
@@ -10939,10 +10951,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40927</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="C12" t="n">
@@ -10971,10 +10983,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41012</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="C13" t="n">
@@ -11003,10 +11015,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41103</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="C14" t="n">
@@ -11035,10 +11047,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41194</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="C15" t="n">
@@ -11067,10 +11079,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41292</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41304</v>
       </c>
       <c r="C16" t="n">
@@ -11099,10 +11111,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41376</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="C17" t="n">
@@ -11131,10 +11143,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41467</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="C18" t="n">
@@ -11163,10 +11175,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41558</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="C19" t="n">
@@ -11195,10 +11207,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41656</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="C20" t="n">
@@ -11227,10 +11239,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41745</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="C21" t="n">
@@ -11259,10 +11271,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41836</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="C22" t="n">
@@ -11291,10 +11303,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41927</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="C23" t="n">
@@ -11323,10 +11335,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42020</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42034</v>
       </c>
       <c r="C24" t="n">
@@ -11355,10 +11367,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42109</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="C25" t="n">
@@ -11387,10 +11399,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42200</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="C26" t="n">
@@ -11419,10 +11431,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42291</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="C27" t="n">
@@ -11451,10 +11463,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42389</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42398</v>
       </c>
       <c r="C28" t="n">
@@ -11483,10 +11495,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42480</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="C29" t="n">
@@ -11515,10 +11527,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42571</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="C30" t="n">
@@ -11547,10 +11559,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42662</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="C31" t="n">
@@ -11579,10 +11591,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42760</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42776</v>
       </c>
       <c r="C32" t="n">
@@ -11611,10 +11623,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42843</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="C33" t="n">
@@ -11643,10 +11655,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42934</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="C34" t="n">
@@ -11675,10 +11687,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43026</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C35" t="n">
@@ -11707,10 +11719,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43124</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="C36" t="n">
@@ -11739,10 +11751,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43208</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="C37" t="n">
@@ -11771,10 +11783,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43299</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="C38" t="n">
@@ -11803,10 +11815,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43390</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="C39" t="n">
@@ -11835,10 +11847,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43488</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="C40" t="n">
@@ -11867,10 +11879,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43572</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="C41" t="n">
@@ -11899,10 +11911,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43663</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="C42" t="n">
@@ -11931,10 +11943,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43754</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="C43" t="n">
@@ -11963,10 +11975,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43852</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="C44" t="n">
@@ -11995,10 +12007,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43943</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C45" t="n">
@@ -12027,10 +12039,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44034</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C46" t="n">
@@ -12059,10 +12071,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44125</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C47" t="n">
@@ -12091,10 +12103,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44216</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44230</v>
       </c>
       <c r="C48" t="n">
@@ -12123,10 +12135,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44307</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C49" t="n">
@@ -12155,10 +12167,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44398</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="C50" t="n">
@@ -12187,10 +12199,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44489</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="C51" t="n">
@@ -12219,10 +12231,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44587</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="C52" t="n">
@@ -12251,10 +12263,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44671</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C53" t="n">
@@ -12283,10 +12295,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44762</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C54" t="n">
@@ -12315,10 +12327,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44853</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C55" t="n">
@@ -12347,10 +12359,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44951</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="C56" t="n">
@@ -12379,10 +12391,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45035</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="C57" t="n">
@@ -12411,10 +12423,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45128</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C58" t="n">
@@ -12443,10 +12455,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45217</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="C59" t="n">
@@ -12475,10 +12487,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45315</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="C60" t="n">
@@ -12507,10 +12519,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45406</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C61" t="n">
@@ -12539,10 +12551,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45497</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C62" t="n">
@@ -12571,10 +12583,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45583</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C63" t="n">
@@ -12603,10 +12615,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45686</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="C64" t="n">
@@ -12635,10 +12647,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45770</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="C65" t="n">
@@ -12667,10 +12679,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45861</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C66" t="n">
@@ -12699,10 +12711,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45952</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C67" t="n">
@@ -12731,10 +12743,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46050</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="C68" t="n">
@@ -12763,10 +12775,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C69" t="n">
@@ -12795,10 +12807,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46225</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="C70" t="n">
@@ -12845,12 +12857,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
